--- a/home/src/Daily_Economic_Report_20260728.xlsx
+++ b/home/src/Daily_Economic_Report_20260728.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="시장지표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="추천포트폴리오" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="주요뉴스" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="핫트렌드예측" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="섹터별수익률" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AI매수추천" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시장지표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천포트폴리오" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요뉴스" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="핫트렌드예측" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터별수익률" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI매수추천" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6280.18</v>
+        <v>6023.66</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.13</v>
+        <v>-10.84</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1468.74</v>
+        <v>1459.4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.74</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -522,14 +522,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.78</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>-8.43</v>
+        <v>-1.83</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -633,20 +633,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27,055원</t>
+          <t>26,830원</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-1.42</v>
+        <v>-2.24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26,965원</t>
+          <t>26,830원</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27,955원</t>
+          <t>27,942원</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -694,20 +694,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>182,120원</t>
+          <t>179,860원</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-1.98</v>
+        <v>-3.19</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>182,260원</t>
+          <t>179,860원</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>194,600원</t>
+          <t>194,480원</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>223,789원</t>
+          <t>223,651원</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -755,15 +755,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15,575원</t>
+          <t>15,560원</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>107%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15,504원</t>
+          <t>15,502원</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -816,20 +816,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30,670원</t>
+          <t>30,330원</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-1.98</v>
+        <v>-3.07</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30,690원</t>
+          <t>30,330원</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32,274원</t>
+          <t>32,256원</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>🔥 적극 매수 (RSI 바닥)</t>
+          <t>👍 눌림목 매수 (스윙 타점 진입)</t>
         </is>
       </c>
     </row>
@@ -877,20 +877,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54,510원</t>
+          <t>53,120원</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-5.19</v>
+        <v>-7.61</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>54,570원</t>
+          <t>53,120원</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60,710원</t>
+          <t>60,638원</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -938,15 +938,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12,185원</t>
+          <t>12,160원</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12,591원</t>
+          <t>12,590원</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -999,20 +999,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>232,000원</t>
+          <t>220,000원</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-8.66</v>
+        <v>-13.39</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>149%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>231,750원</t>
+          <t>220,000원</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>275,962원</t>
+          <t>275,375원</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>317,356원</t>
+          <t>316,681원</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1,630,000원</t>
+          <t>1,550,000원</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-10.24</v>
+        <v>-14.65</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>138%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1,629,000원</t>
+          <t>1,550,000원</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2,052,150원</t>
+          <t>2,048,200원</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2,359,972원</t>
+          <t>2,355,430원</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1121,20 +1121,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>376,500원</t>
+          <t>364,000원</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-6.58</v>
+        <v>-9.68</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>380,000원</t>
+          <t>364,000원</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>443,150원</t>
+          <t>442,350원</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>509,622원</t>
+          <t>508,702원</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1178,24 +1178,24 @@
         <v>168300</v>
       </c>
       <c r="D11" t="n">
-        <v>-6200</v>
+        <v>-8600</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>124,200원</t>
+          <t>121,800원</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-4.75</v>
+        <v>-6.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>124,400원</t>
+          <t>121,800원</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>144,225원</t>
+          <t>144,095원</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165,858원</t>
+          <t>165,709원</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1243,15 +1243,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>221,500원</t>
+          <t>210,000원</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-1.56</v>
+        <v>-6.67</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>215%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>197,595원</t>
+          <t>197,170원</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>227,234원</t>
+          <t>226,745원</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🚨 전고점 터치 (전량 매도 권장)</t>
+          <t>🛡️ 관망 (시장 변동성 확대)</t>
         </is>
       </c>
     </row>
@@ -1304,15 +1304,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1,551,000원</t>
+          <t>1,549,000원</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>259%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1,563,000원</t>
+          <t>1,549,000원</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1,409,400원</t>
+          <t>1,408,700원</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1,620,809원</t>
+          <t>1,620,004원</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>🚨 전고점 터치 (전량 매도 권장)</t>
+          <t>🚀 거래량 급증 (수급 폭발)</t>
         </is>
       </c>
     </row>
@@ -1365,15 +1365,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>172,100원</t>
+          <t>165,200원</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-0.29</v>
+        <v>-4.29</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>173,135원</t>
+          <t>172,795원</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>199,105원</t>
+          <t>198,714원</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>124%</t>
+          <t>125%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1548,20 +1548,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6,540원</t>
+          <t>6,240원</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-3.82</v>
+        <v>-8.24</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>369%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6,450원</t>
+          <t>6,240원</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6,879원</t>
+          <t>6,863원</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>👍 눌림목 매수 (스윙 타점 진입)</t>
+          <t>🔥 패닉 셀링 (과대 낙폭/적극 매수)</t>
         </is>
       </c>
     </row>
@@ -1605,19 +1605,19 @@
         <v>5060</v>
       </c>
       <c r="D18" t="n">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3,455원</t>
+          <t>3,435원</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-4.95</v>
+        <v>-5.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4,145원</t>
+          <t>4,143원</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1914,15 +1914,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>317,000원</t>
+          <t>314,000원</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-4.8</v>
+        <v>-5.71</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>333,750원</t>
+          <t>333,375원</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>383,812원</t>
+          <t>383,381원</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1975,20 +1975,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>399,500원</t>
+          <t>382,000원</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-7.31</v>
+        <v>-11.37</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>400,500원</t>
+          <t>382,000원</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>438,950원</t>
+          <t>438,025원</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>504,792원</t>
+          <t>503,728원</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2032,24 +2032,24 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>-6500</v>
+        <v>-8700</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>104,000원</t>
+          <t>101,800원</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-5.88</v>
+        <v>-7.87</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>104,100원</t>
+          <t>101,800원</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>116,860원</t>
+          <t>116,735원</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>134,389원</t>
+          <t>134,245원</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2093,24 +2093,24 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15,135원</t>
+          <t>15,070원</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.03</v>
+        <v>-0.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>128%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15,105원</t>
+          <t>15,070원</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15,444원</t>
+          <t>15,439원</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2158,15 +2158,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13,100원</t>
+          <t>13,050원</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-0.04</v>
+        <v>-0.42</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13,445원</t>
+          <t>13,442원</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2219,15 +2219,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10,020원</t>
+          <t>9,990원</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-1.09</v>
+        <v>-1.38</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>111%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>10,080원</t>
+          <t>10,078원</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2280,15 +2280,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20,800원</t>
+          <t>20,400원</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-2.58</v>
+        <v>-4.45</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>148%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20,967원</t>
+          <t>20,955원</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2337,19 +2337,19 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>184,400원</t>
+          <t>181,700원</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.99</v>
+        <v>-0.49</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>176,795원</t>
+          <t>176,675원</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>203,314원</t>
+          <t>203,176원</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>84,800원</t>
+          <t>82,200원</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-13.38</v>
+        <v>-16.04</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>189%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>83,900원</t>
+          <t>82,200원</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>88,665원</t>
+          <t>88,470원</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>101,964원</t>
+          <t>101,740원</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2459,24 +2459,24 @@
         <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>-34000</v>
+        <v>-50000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>187,500원</t>
+          <t>179,500원</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>-8.31</v>
+        <v>-12.22</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>187,600원</t>
+          <t>179,500원</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>221,140원</t>
+          <t>220,735원</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>254,310원</t>
+          <t>253,845원</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2524,15 +2524,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1,201,000원</t>
+          <t>1,183,000원</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-1.56</v>
+        <v>-3.03</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>122%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1,127,950원</t>
+          <t>1,127,100원</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1,297,142원</t>
+          <t>1,296,165원</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>🚨 전고점 터치 (전량 매도 권장)</t>
+          <t>🛡️ 관망 (시장 변동성 확대)</t>
         </is>
       </c>
     </row>
@@ -2585,15 +2585,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>303,000원</t>
+          <t>296,500원</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-2.88</v>
+        <v>-4.97</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>310,775원</t>
+          <t>310,250원</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>357,391원</t>
+          <t>356,787원</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2646,20 +2646,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>725,000원</t>
+          <t>705,000원</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-9.029999999999999</v>
+        <v>-11.54</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>124%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>731,000원</t>
+          <t>705,000원</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>847,150원</t>
+          <t>845,850원</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>974,222원</t>
+          <t>972,727원</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2707,15 +2707,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37,100원</t>
+          <t>36,500원</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-3.39</v>
+        <v>-4.95</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>36,145원</t>
+          <t>36,112원</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2768,20 +2768,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>180,200원</t>
+          <t>175,500원</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-9.9</v>
+        <v>-12.25</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>179,300원</t>
+          <t>175,500원</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>204,825원</t>
+          <t>204,555원</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>235,548원</t>
+          <t>235,238원</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2854,71 +2854,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 21:49:00 GMT</t>
+          <t>Tue, 28 Jul 2026 04:59:57 GMT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>중앙일보</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[글로벌증시] 뉴욕증시, 유가 급락 속 혼조 마감…반도체주 하락</t>
+          <t>“주식 대박 배 아팠는데, 투자 안한 내가 승자”…포모 가고 ‘조모’ 왔다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE0xSG1UWEVTRDFqRXJXaHVkM0dYYlhoNGswbk1uS0NVNlhvZzN5bjk3ekNfejVSV2ZybmVDejZRRV9MR2NtMDVNd0Vod3VHYnhyNzlHVVk5WkFTTEs4aXJMLW1VdDJIYVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5CemxKUVI1TFZrdVZTRXp2VGxTc3lvTmxyOGdYci1NdnFsNXZxNmkyTFVRdUZBVjhtblhaVmlGRkdJN1JNd19LZHFwTk9BMUI4eDZtY1NB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:03:00 GMT</t>
+          <t>Tue, 28 Jul 2026 07:25:10 GMT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>머니투데이</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[경제]CXMT 상장 여파에 흔들렸던 코스피...오늘 증시는?</t>
+          <t>"주식 시장 이게 맞나?" 통곡의 개미들…코스피 -10% 대폭락 - 머니투데이</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE40SUJ6czZSZjdwSW9yaV9FYkl3eVQxR3FEcURFMlIteHVpLTRYR0R6cjRpNU1rN3A4ZWlZU0EtczdQSjVPRW0wX3d6eng5SF9uNUpTOHEzYUZHNGJlU2ZFMTNNenJVM2haR3FHTnIwTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9OMXY1c1RBVHQxRkQyMS16blZUcE4tVHE1eXZMOS1GZVMyVzQ5dHRUV3RlT215Q2ZSak5ZYTctSGlEUE8xZFdfQXRBQW16NVgxdXFtOEd0cjVsLVBLMG1heTRmMURWQUJl0gFuQVVfeXFMTmQ0OXA4T25BaGlrbWNZd21lb3JNSnBtS2g3WWk4dGRRUjhPb1ZYVS13aEh4Sk94ckxEbVU4Um1kNnUydnZxWjNfX1g4SWU2UkQ1a2xtOUlBaGRYaWQxclhSREJFaUlhVWZySjV5TEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:05:27 GMT</t>
+          <t>Tue, 28 Jul 2026 01:36:24 GMT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>주간조선</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[굿모닝 증시]美 반도체주 급락…국내 증시 하락출발 전망</t>
+          <t>또 '검은 화요일' 덮쳤다…코스피 8% 폭락, 서킷브레이커 발동</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2928,14 +2928,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBkZmhOUFNSUjQ4Y1g2dVB5dk10YWc3cWp0Z3V0V2NFWDhySFMzbkNDbDUtV2xDa1F2ZEJ6X0xMa1hyaGdvWmZYS29ZallsU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9wSDhieXV6VERkTGU2MGhBTjJST2tNcUxRN0VDbGlleU5PeWRraGthVTdYbmxDcUlaRTljTkNZZmdZaGhySFRROXBMd25YckFEU2hkRHJRaXd0SU5vWWNQc0hoZFJlMWJfM2fSAW5BVV95cUxONFN0OFYxSUFxTkhRNnRRY2I1azRYel9TZHJhLW1vazhDdG91V1ROdWJKNkxjR3pCd25xWTBFdlV1OTFtcGpZUDlUOG9nOGJpMWZLY1U5d2oxOTkzWFhTOXBuWnM2UmY0VzE1RUxQQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 21:07:13 GMT</t>
+          <t>Tue, 28 Jul 2026 05:02:00 GMT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[뉴욕증시] 예전만 못한 엔비디아 투심…혼조 마감</t>
+          <t>[증시 긴급진단] "반도체 PER 3배는 최악 반영…더 내려가진 않을 것"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2955,24 +2955,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4zYmhfOFZaX0V6dXFiZUd6WjhIcGhFRHV5bURLNEdOVDYtR2ZYeXFTMEhxQmNGMFJMWGZyeXIwdXpwaXh0NWRMNFJacU1qZUFKUHpwRTRvc2ZfV3N1b2NueGZEaDduejZYcmdNaTNZeDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE50WXRyZlc4eWJ2bVlVenk5WjEyWlJkN2JaaDI0VFk2bjFiSlk5WXo0Um1iMjdHTXFyaTBQaUdGM0NlZjY1S0gyZlE5N2dYaFVHMzl6UFZrTi1BdWhjQzNVMGl1WmM1V25OTFJBWW9OblM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:02:00 GMT</t>
+          <t>Tue, 28 Jul 2026 04:55:55 GMT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>국내 증시 출렁이자 ETF 시장도 한 달만에 90조원 ‘증발’</t>
+          <t>니혼게이자이 "日 주식 격렬한 등락 일상화‥한국시장 영향 커져"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2982,51 +2982,51 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQOGlLZWUyU0hqUm45a1JVNTNhcm8zS2dKZ2xBSVBYSjl4RFRHeVpYbF9RcVk4MTkyaEQzWG9GODFxeDdTelNRdFF5WWhNa3pqcm05dlJPRzRyU1M3SGg4Ym1OcVF1alFxZzZsMWN4RkJwYXp4T3RXaFFXQTFVRkdxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE95dU9iNEZkRGF2WmpYcXlhN2lkNEEzdk92RmU2U2dHWGt3WnhzSEVrUm9oem1qdk0tdTdxc2Z5b2NNTllOMEM0WTlpb1Y4Wkh5Q0xVenladGVCSjc1LXVfQ21hS21vMUoydHRlYXRxTm10WFJl0gF0QVVfeXFMT0x5Y1duek9zNGtFcWlURG5yX1pzZGdfbEQ0b0VzdVZBWXVnaGZhVVJob2dkcGZNYjJvR2hKSjRDNENYZzNCMG9Tc2Uwd3NLTm5aR1h1VzNwSlZpZW1yTGZNU01GOUUxTjljcUltNkJsNk1PVVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:44:37 GMT</t>
+          <t>Tue, 28 Jul 2026 07:20:05 GMT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MBC 뉴스</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>유가 급락 속 뉴욕증시 혼조 마감</t>
+          <t>증시 폭락 '검은 화요일'…코스피 10.8%·코스닥 7.7%↓(종합)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBTUklGWWQxeVRUU1ZEN2h3Z29QTG13VXp1aVVaRmVEb0tjWDhjYmMzM2xDM3FQLXJlNlZ5Y29ReGs3SjJMOVJUbU5ZUDdXNVJfRmJuYUhjSW9KZ2UyaGM0LXM0OHp0eTJtU1ZvWG10YUVSaS1obDdOTzB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9PM0xJcUR0OWVweVNMS19DWUZJOVNGQXVpZ3BLSzNxWWltYk9Jek13dXRZbkpVaGZkUjVLV21aLXJlOHBMMkNqXzRXRHZObXp1SWszRk1nU2JZZGvSAWBBVV95cUxNamRXSGpkQVhVNVdZaU9nb0M1STRnV0plLXp4NGlMQ2h6ZkpuX1ZvNGYzXzNtNk0tMEI2S1A5UTRDQkJONnB4YlJLNGRDSldPTVNlQlZZYkFKejhHNUVKWnY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:44:00 GMT</t>
+          <t>Tue, 28 Jul 2026 01:43:43 GMT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>경향신문</t>
+          <t>대한민국 정책브리핑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>뉴욕증시, 유가 급락에도 반도체주 약세···S&amp;P500은 ‘보합’</t>
+          <t>이 대통령 "한-브라질 동반자 관계 도약 원년…경제협력 기반 강화"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE52ZExTNDV3ZFVwdmc5SU5uUTBEbVhJSzRqS0ZNVDJiYVZRM1lGZTAtOWJ4cjVDcENLQ1Q3OVp5Y2xNamh5djJHS0hFMTJyc3NadkZ4VW01VVJXZ9IBX0FVX3lxTFBkUTJyNFF3dVA4S1BqQWdhVnJBc19Jdnh1ZnVVSVJQaXhyZERPUUhVTVlZZmFsVUtLcHZjUXJ6d3g5aEVXaXF4em5uVkFOZXlDWmswaTZhaFJVd3VkVFBz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5zLWN4bUtrR0RIekt2RGtKN3hOeXVEOHMwRHlTd28wZFR2bGhUaV9UOUJkZ0hIZE1aVHR0M25MZjB3SDhFeHRZMnU2STN0dXVEM1NjUE9PRy1DNlU2Uk12cnVRc2xWaV85dVJsZA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 21:15:00 GMT</t>
+          <t>Tue, 28 Jul 2026 05:56:00 GMT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에너지경제신문</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>환경부·산업부 조직문화 충돌…기후부 인사·운영체계 재점검 시급</t>
+          <t>[증시 긴급진단] 겹악재에 무너진 코스피…"과매도 구간, 투매 자제해야"(종합)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3063,95 +3063,95 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5lZmhyX0NMU09ZZUE5dXhNVUliYlZOTUFWUHlXcHRkb1dLZ0ltSTAyay1FWC1nYnNJNDJQbTd1WGZJMkUtNGNjLVp6WXFHYmVPRHllb3hBNFhwZmthRDA1YlJwTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1VMk1jNlRhbGZrMmp4Qm9WRElzMHdXRlZxTTlNeURpQ0lSMnZab09oc1dVMUhHV3YzNm9ONjJlNTF0NG1PLUdqdzVZdFdhbzhJUFNCVWtCU2RqY3hCdm4tdTNKeE1MWGJ0ZEtwekZ0RXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 20:11:40 GMT</t>
+          <t>Tue, 28 Jul 2026 08:51:00 GMT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>연합뉴스</t>
+          <t>조선일보</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>뉴욕증시, 유가 급락 속 혼조 마감…반도체주 하락</t>
+          <t>요동치는 증시에 野 “코스피는 ‘도박판’, 코스닥은 ‘얼음판’”</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFA0NGtnWnZaQ1RxcWZiQl9jQmV3YklmYnBJYzdMRU5yY3hNZDB2bF81VkdqOG9lM0pZT1UtZVlEYW52T3pmcHg4NVRWXy1BZEhjMlYxT3VIeGhGMkXSAWBBVV95cUxQWHlLM0I2NXZXZUY5eUlOakluODlZQXRKRGlOX2JtRjkzMlU5OE5YTkg0ZUg1amVCUldrQ1Y4YktOQlhVZUdxUUNZM2g0Y2lBc0QzcVRyUzZTdjRTMld5VFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxORFN2aDFpdTJyeG1fc184WVR1eGJLbmNBVTFodFB5TFJPOGZnQ2VwTXV0NVd4RG9YSkE1NVA2Y0RoQk5QcGV0MmZIOExULVpjVDNPV3JwSy1KWUE3Y3VHRGxjREpFZG9oYVdmTUMwcmFrQUhvLU0zaWpxeWpnNHVaUkpwVWpfZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:49:00 GMT</t>
+          <t>Tue, 28 Jul 2026 03:03:12 GMT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[3분증시] 뉴욕증시, 유가 급락 속 혼조 마감</t>
+          <t>'중국발 반도체' 쇼크‥증시는 '검은 화요일'</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1JaVVVS1RGaGpjakpXbWJzTmxyMWRka0ZzVHZvQkpXclZZM2Y2ZUNmMlRPMnhXX0I5RFVLT1VEbTJSU1VNV01EcVVOVmJUTWlCUk5Hb0V2dTlWYjRwbzB2cDZxYWczUFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0xTGx6cl93UDBYU2xrcDZMSzEtZXBHVm9rWFAwazBzX2hrUnpGaXlqa0l5Znp4SGRBbVpONmNjQTVvQldQSzZfVVo4VDdic0tiLThJcnJPVjFBUUxBOHdTalRNaGpoZi1NckRLdnNfRUtWY2F0d2hZZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:37:00 GMT</t>
+          <t>Tue, 28 Jul 2026 07:10:34 GMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[스타트 경제] 한 총리 "가계 순자산 중 부동산 비중 71.9%...해결책 마련에 큰 책임감"</t>
+          <t>[증시-마감] '검은 화요일' 코스피 10.84% 폭락…6,000선 겨우 지켰다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBiRjEwTmFKaHBKXy1Vd2ZRVHNydnFELVdTeERyMFFvYTR5TFg3b3ltNFNwdHpsLWtUSjJSak1LaUVaR2U5elJvMlNmai1nOS1jNDZCZ3QtN3MyeTdmSkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE4zdTRzX2M5bjh4NmhqclF0Uy12YlBuejZHdFplWjgxaVUyNVFTMXZjMDlVdTMtb1JHRm9PdU1MMGl0Ym40S3FWLUl0T1VVUDZrOTFyLVd0UkdudmdmV0pLYVhOTkJmTFNPQnlHQWhhcVM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:29:55 GMT</t>
+          <t>Tue, 28 Jul 2026 07:01:00 GMT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S&amp;P500 선물, 빅테크 실적·FOMC 앞두고 하락…美 국채금리↓</t>
+          <t>증시 폭락에 수요 폭발…개미, 단일종목 레버리지 7천300억 폭풍 매수</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3171,24 +3171,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9wdTZHSlN1el9yZlhJeHdCU01NcHJ3TnkzbVQzNnR4YXNMTjFvQkpOUi1SZVRJY1NSblh4ZkFvWkVVaEVCVUJhUFZkRHJHcjlBa0xPQVRkWUZmOEI2TzNmSTlHRDFBc1pVMUlmYTV5MFI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBUUFhPOU54dHRBWWJXbHY3Z2RxZ3pUZ1Z2ZjFuczJJMGREZHdSY3Jab3FIV0pkdVo4d1VfUzV0RHljVXRXUlR3cDNIQ1VRU0dJaE5Dc3lTZkkzS3d5eGZVTDMyNngzV0lhVXp2RzNiN28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:06:00 GMT</t>
+          <t>Tue, 28 Jul 2026 04:33:00 GMT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SK하이닉스 ADR 해외주식 순매수 1위…세금 더 내는데 왜?</t>
+          <t>[증시 긴급진단] "악재가 한번에 겹쳐…1차 지지선은 5,000선"</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3198,41 +3198,41 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPcTVnSS1nMm1RQWVUdWNBclRrWjZHUjBKMURWazhZQThuNExuZWhtaEVBXzhYVlhNM0xJb3VLc0t0QTE3Rm9KOE5pYVNJSlVweW50MkhvWURKRzJFSzNvZ3NXc1RNVGRqdFl3VTllVkpYcWpUZENCYko1NGwzak9OU2MwYm5qS0pDT1NJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1RbWpJQzM1YjZLLUthalZMTHg0TUc5SkRVQ0wxc0p6cF9ZR0E0TkxmN2ZUQ3dZVV93aS1rQXJtVkhhZ2dzLXA5WTlUelh2TWJHYkd6VEdIUF9DdWszdjlndFplZ0Zia0ppZHowVVRMTTk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 07:51:02 GMT</t>
+          <t>Tue, 28 Jul 2026 05:33:30 GMT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“내 주식 도대체 언제 오를까”…증권가 “V자 반등은 어려워”</t>
+          <t>[증시 긴급진단] "과도한 낙폭, 저점 논의 무의미…반도체 우려 지나쳐"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5OdDFwb1RtcDBOY0wzMWszUEtkbXI1NlRhSDlMeXNoT3F4ODFZbjZiV0FrWHV2THBsWi1JMWE0SWhfdENMeHJnZTRickNVWWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9uSDBxbzFwY2MyRkRWY2tjamJpTG5kcDFkQjA1QzQyVUF4aU0tc0sxczFsRUkwU3ZqUHlhNmJfUFRFd0hXYmdnWGRNN2htLUtRX2I0cnU1M0pWQ2QyQWdySkxyVGNSN2dTSEFQOHlUYWE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:56:05 GMT</t>
+          <t>Tue, 28 Jul 2026 10:16:36 GMT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3242,34 +3242,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BofA "美증시, 역사적으로 8~10월이 최악의 3개월 구간"</t>
+          <t>[亞증시-종합] 반도체 쇼크에 中·日·臺 하락…홍콩↑</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE45MFlJMGtzOEpQLURWQm96eDhRajVJYnVscXcxMkFvMFE0cEQ3TFhhUmRybFlHUDNJeEV2MUlMQXE0VGcyc0ZxWFRBZXQzVWVsVFpoeERNc0FYMlZEaGpFSDVwajhNaVp0YVd4QXROOFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9NYUJvZlBtUHdIckhpUUxORXlKMXctUVVtRGhpWWFSYkZldVo1SC01T1BIZTBweDVSVFJsZHhFRUhGTjgwMVFFME9jdlVLUGN4NDZYQ2JvQ3VUdi1zRUNSbU9FM2I0YkotRmFEdm9FQVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 21:11:00 GMT</t>
+          <t>Tue, 28 Jul 2026 09:39:17 GMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>연합뉴스TV</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>뉴욕증시, 국제유가 급락 속 혼조 마감…반도체주 하락</t>
+          <t>[중국증시-마감] 반도체·AI주 약세에 하락</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3279,51 +3279,51 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9vTHBlLV9RWkREN1d4V2V4Z2k0SHV0VW4wVHRyNGl2QzZURUZUY083cFhkd1FoWU9WWWxYZ1FvOERReUxkTXVIaGtmUnM5bHBzcGpXYzZ3Z3hlWG1hUDJEeUlUODhTUmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE00MjFxT2FKTmJqT2dRdzFyXzl6eHpjWkVPZUNrMWFsM3BKNjZ0UEptYVRESzBhY0Nfdy1YRkdOMTU3SFB5OEdCZHk3NS1qMTI2VDBOZWQxdmFTZmFVTkJrNDAxdGV2YjZiTmRQV01PejY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 19:41:52 GMT</t>
+          <t>Tue, 28 Jul 2026 07:21:00 GMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JP모건 "S&amp;P500 지수 상당한 상승 여력"…증시 강세 전망</t>
+          <t>'검은 화요일' 공포에 질린 증시…전문가들 "과도한 낙폭…변동성 적응 필요"</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>긍정적 (호재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFA3R2JXemlYOWtyU1gwR0x2aDdjUkhRMzhIdTd4d1BOME5mb1JxM0w4dXp0Y2lmckpMVmNMcUFyOGVLaWxhWEFWQkhJZGtpbUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1pb3lXLVYwLU9aTVp4MU1vMFJhaUFZQWtyRTlKblM1M1BVbTVod01QeWU0cnc0ZS1GZThVWjBEUk52Vm9QWVVOVlFQb1kyMDh3d09uSUZPcDdBd1hzY2xlRHY4WF9vN0xvcU1oSWVfUDU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:09:00 GMT</t>
+          <t>Tue, 28 Jul 2026 01:52:00 GMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YTN</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7월 28일 화 경제 캘린더</t>
+          <t>"코스피 변동성 키운 쏠림·레버리지, 美 증시도 문제"</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9hbWhDdkRQX1lwQnJMOC1TNnhWSXdSUHN3NXJobXBJZEtlMlJrMXNPRENOZ0p2VUp0MElFTXJqbkFXQ2NRb3p2UjhOZ2ttV1g1ajdUM055V1p5cFBTalE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9OMVExU0haWXVzOE41QmlyVk1URFVsSkVnWGtheEZoTmdQcE5naDZpLVhhaXRvdjJtRjNUOUtmN2duYVhLNFFTVU1oeTIwd1VaVHBTdU96TUVMc3VlUEx4cFlHSnNidFU5MVFqSlVlN0Q?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:11:00 GMT</t>
+          <t>Tue, 28 Jul 2026 04:55:19 GMT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>조선일보</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한 달 새 정기예금 21조 늘었다…증시에서 예금으로 역(逆)머니무브 움직임</t>
+          <t>[증시 긴급진단] "중국발 악재로 반도체 투심 급랭…투매보단 관망"</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3360,78 +3360,78 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNQVZKT0NWOWI0bjNvTGFpbS1iS0RDdlRydy1iZTJQMHRIMXd1QnJwSVNnRXMyUXVUcHZYUFhVZmdMRm5wMzhoT1VkajlpT3gwem0wSHNRNEd1TnRPSUFwVGczOWxQbC1EWmZpWEN6dEZ6WHA1VENFYlVqOFhVOXA3V1hEZFNzS25pNnVhdUV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1nckF5VDdaZ2VHWmE3OEhGSVkyeDNzR3NQVDVzWm9LdUFBRW9pYUlPUF9Yd2NKZmNPQUpTWmNjRHRydlhTWnlpT2tBbzVHcHhRUDJVaENnWDBycTFZLXV6X2hVelFfdk5YWEF1V0kxekE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 20:47:50 GMT</t>
+          <t>Tue, 28 Jul 2026 05:28:44 GMT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>뉴욕증시, 유가 급락 속 혼조 마감…반도체주 하락(종합)</t>
+          <t>[증시 긴급진단] "AI는 가보지 않은 길…변동성 감내할 포지션 잡아야"</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5ybVk3ZVpRLW1iSG11N1plUWRxazhjSnFNQnlUN1Z1MF9wSkgwcG5VeEJpOHZPN2Fxb2l0MHp5aFVIZmJnblU1eHhsNk5lTm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9VaGlQVFdoa3BhWTQ5S1JCN0V1SC12bjdNUWM1UTN0cHNkVFNGS0hGUFVKUmhBd0RtVlZGeDhpaVByUFlZc0E0S3BPSjRVclJaYWhLT2o1eHRySVhvc2NkM3M1SmZGbWx5R1Z5bFFuOFk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:46:00 GMT</t>
+          <t>Tue, 28 Jul 2026 06:33:44 GMT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Investing.com 한국어</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[개장] 뉴욕증시, 반도체주 부진 속 혼조 마감..엔비디아 5%↓ By 알파경제 alphabiz</t>
+          <t>[속보] 증시 폭락 '검은 화요일'…코스피 10.8%·코스닥 7.7%↓</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE43ZGVoOGRvRVM3aXctcllYaVRHd1BVXzNFUnY1UnE3MHVRbjNOeWw0TlZtN3VUZ2s1c1VHZVkxLTJHaUFWYmNuWnJXeUZacGhVWnZyTGhFbHJ0SktxcTA0Mm0tM2lGZll1M3RlMzFCU0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBVVzhmZENRSVM5QWlRWHNnZVFiSFgwajN6RjcxeEc2SDBTX0ZMdlY4LTNZQ0g0dHUxQjI0MTZDQ0c0cGRKZFRobFh2OVdDbEZyWVhfNnVVYWtKVGcwWl9aR9IBYEFVX3lxTFBVVzhmZENRSVM5QWlRWHNnZVFiSFgwajN6RjcxeEc2SDBTX0ZMdlY4LTNZQ0g0dHUxQjI0MTZDQ0c0cGRKZFRobFh2OVdDbEZyWVhfNnVVYWtKVGcwWl9aRw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:46:00 GMT</t>
+          <t>Tue, 28 Jul 2026 07:21:19 GMT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Investing.com 한국어</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[0728개장체크] 美증시, 유가 급락에도 반도체 약세에 혼조 마감 By 인포스탁데일리</t>
+          <t>공포로 뒤덮인 증시…'美中발 악재' 연타에 코스피·코스닥 추락(종합)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3441,78 +3441,78 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9qTEVvNEdTLUd2THhoSEcxVkhRaE54Q2N6OXdrM2xCcEIwVk1KbE95TEV2bkw0cjVkWTctMmZ4Z0Rway1tRlMzNHdlVjhLYURfdU4tX3JlOGQ5c1BxR2VNbTU0eGp1dV9Ia2hGYUkyVWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBwbVVjazM1RzRxck1oQWdaMnptNDNMWTNBYjdEbDVNZXUtb3dEUWF1VFgxQlNFMUJjT2pjT1FDUlRjY1BFQ3BzV0VtcnVHSUZEbU93dmY4bnBnazMyM2dQLdIBYEFVX3lxTFBwbVVjazM1RzRxck1oQWdaMnptNDNMWTNBYjdEbDVNZXUtb3dEUWF1VFgxQlNFMUJjT2pjT1FDUlRjY1BFQ3BzV0VtcnVHSUZEbU93dmY4bnBnazMyM2dQLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 20:59:00 GMT</t>
+          <t>Tue, 28 Jul 2026 08:06:03 GMT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KBS 뉴스</t>
+          <t>MBC 뉴스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>뉴욕증시, 유가 급락 속 혼조 마감…반도체주 하락</t>
+          <t>오늘의 증시</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>중립</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBaUUpUdFpHNG1vbzhIMWpfd0hwOHNSWTM2SnctNE1NcFR3TGtmS2ZyaDJTWG96bG50NEJGNzJxVFhETXBmNzhJN3pEZ01HVDI5RnNZc0toMElJODg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBUenhWYmV4Y29FN1hqcFZUQlc1anlHUmVHV24ydXAxQmJVU2dpRHVKbV84MkxUVWtuR1N1T2RhYWIwTGJnaDNlQjl1QVFUa2ZjcTM4TmNxVFNLOXJvYWpEOWowd29xTFF3Y3gwYjgxZ2pPaUYweDB6Qg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:18:38 GMT</t>
+          <t>Tue, 28 Jul 2026 09:20:58 GMT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>연합인포맥스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[아주경제 코이너스 브리핑] 美 기술주 급락에 투자심리 위축…비트코인 6만3000달러대로 하락</t>
+          <t>유럽 증시, 장 초반 상승 출발…유로스톡스 0.43%↑</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>부정적 (악재)</t>
+          <t>긍정적 (호재)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5EdWJBVi04R2RzMk12WWQ4TkJOOGp3UDF0bUljWUtlMnBjbkkzTGZZWGFQVW96R3B5OUVtYTh1MGVJYWw0bTNqWUdPbXY1QzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA5Y29DbDdVUjNPM3ZyTkNBNnRBZ3MyNnJVVkJrRk9sMy1aODRsMmg0VWRhRkZWZHdDcGNvTXVYNG1SQjBwRngxRFJYb0xJUEwtNFVvZjJHZVpEOHctNEdEMFpUNWV4NzJDVkUwVDFrVE3SAXRBVV95cUxPX0lLSE90RHB1dTB6ZnB0Nm5vMjFidW43TVNTT3dTT2Q4b0NiZ21EVFVadWRqejlsREh0Q0xpYnl5am5iZUhwcTVTZnFRVlBpRXFWT2gxTENDUHlhbTUyM0ZFUUtlaG95T1FzMjNCanpHQzE2aQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 22:04:19 GMT</t>
+          <t>Tue, 28 Jul 2026 04:48:56 GMT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>v.daum.net</t>
+          <t>대한민국 정책브리핑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[아주증시포커스] "급락장에 데인 개미"…미수금 한달새 절반으로 '뚝' 外</t>
+          <t>힙한 문화 나들이…'인생독서×인생서점 북페어'</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3522,24 +3522,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5WLS1qNVllLVFORFVCUmQ1VkJaTk5CZ1hYMUQ2UHktT2NfSDZJWUNjLThvakFHSDNvWGpzdlV0ZENVaUpXRGc0MmdyN3hGWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9mQ3VicGFVY3pydTJkMzlhRzU3aHRtWUctMGhPcFlwZHk0NkhhVzduZ25COWpOLUtGYXY3Z0NiejFWTHd2S3I3M2RESVAyWkppaHF3OC1FVy1EWWhMMjV1RkpYbjVTb09XSFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 23:31:58 GMT</t>
+          <t>Tue, 28 Jul 2026 04:13:14 GMT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>신아일보</t>
+          <t>연합뉴스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[뉴욕증시] 반도체주 매도세에 혼조…나스닥 0.18%↓</t>
+          <t>[경제읽기] 또 '검은 화요일'…코스피·코스닥 동반 추락</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3549,51 +3549,51 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9vU3pUb1EzdFpnZmpfUzlNcEsxdEwzNmtBSWVWWjhPNk96aUlqRzYyYml5RG1oZjJVRnhQUlpEaHJKWHVhN3BFR1ZiMlBnSThzRmZ6dmM1bUVJRzdjV05Wc1JrNC10VGJOSDZILVJUOVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE92SS1JdjR4c0NtWVRUOUVxeVpOSGI1SmN1OFhRdHRCZnlCcHVMZHpjNlZ6ZDk1TlNEMFMyZGxzSnlnSk0xc1Q0bXpScVlISmhEaWRMYmNCVzFmaF9BaUJyTNIBYEFVX3lxTE92SS1JdjR4c0NtWVRUOUVxeVpOSGI1SmN1OFhRdHRCZnlCcHVMZHpjNlZ6ZDk1TlNEMFMyZGxzSnlnSk0xc1Q0bXpScVlISmhEaWRMYmNCVzFmaF9BaUJyTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:25:23 GMT</t>
+          <t>Tue, 28 Jul 2026 02:48:00 GMT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>머니투데이</t>
+          <t>YTN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KR모터스, 주식병합 거래재개 첫날 5% '뚝' - 머니투데이</t>
+          <t>반도체 쇼크에 증시 급락...코스피 서킷브레이커</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9fb1UwTUF2SnFkWFZYOURBbkUzdDFObXZMemNZZGpZQURtMUsyNE9lS0FGa3dobVQ3T0F5Wk5sOGJSNlJzaU9ETnN4VTk0d1ZLYTVhdUxDclBrUHBhc19kTzM4ZWpBLXFN0gFuQVVfeXFMT3pULXduV3JjRXowNWNhd21zY1MyUm5leTI0SFFJeWxKQTBrZUxob21leWRZVXU1Mk5Pb1QxaHJDVkdfS0pSaGFmb3lOUmpya0dTODdaOHVSYXBjcGNjdHpnYWRMYU4ydG8yZHpBLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBUNGw2LW9WbHEtTG9lZklBRU9mN2RXTWFaRVNWMGNlWDdvVENPR0MtdzllMnlUY0FyM3FTY1puYmc4U0pvUnVSQmh6NDhWOGdWODFTb052SjhEeTFMQXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mon, 27 Jul 2026 19:30:00 GMT</t>
+          <t>Tue, 28 Jul 2026 09:12:17 GMT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>동아일보</t>
+          <t>주간조선</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2배 레버리지에 ‘홀짝판’ 된 증시… 43회 멈추고 1.8조 강제청산</t>
+          <t>서킷브레이커도 못 막았다…코스피 10.84% '뚝', 역대 두 번째 급락</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3603,61 +3603,61 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5sQ3MzbzktbUhEMTBGWEt4Q2hldWNWRjlMc1BneXFwb3hQUHlpdW9qMDBsbUM0MzV3dWxlX21BblBqN2E3a3JZX0s2RTJkX1NhVFBSVndIaUxTbGdrT285QzBucWFpdkhyeFdZVUtuUTZ5SW5lVVHSAWZBVV95cUxNSnRUYzhFSWtYVVV0MXAxemNyLWpaYThZQ1ZBZUUzR3BJS2ZnaHF0eFJZaFZwUHo0WDVOSmluSHowckE1ZzlyS3E2c0FLWFFhSkpkOWd1SC0zd2ktWXRWMjVlR010REE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBqc2dqQUlpVXp4WEM1VmhvaDZvaG9CMC1uWTEycEVXQXpnbXgyMEtCNlA1ZUF2TUVzQ3RFaS03WXBNSE1xeVllbkl4aThkOEpYMnVua0NZaUJmNTlqWGMxOHZIY1NHRXBxemfSAW5BVV95cUxOOWJmbTk0Nk1rZXhPZVg0clVyVkhMdDZUa3FlR1gzMWhONGphT2dJaG5MeXNPOEtFXzNtRXJDb05nMWd2eUhUWFBGTmZ3RmR0Zl9DUzU1OUtIOWY3TEo0U3RVamQySl9rZjlOZ3M0UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:33:28 GMT</t>
+          <t>Tue, 28 Jul 2026 11:06:48 GMT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KB Think</t>
+          <t>서울신문</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[7월 5주차] 금주 국내외 경제 전망</t>
+          <t>창신 상장 이어 ‘노광장비 양산’… 中반도체발 증시 쇼크</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBYUGF3REk4aGpwbzhLeGVSS0RmUTM5YWt3QmhIMDBkUHhYSVVqS0pzVVFrLVZab1RWRkdwRk9KS2xHODVMNmNYZjBJU1hlQjNhbUdBcnFzWmpmbk9UTmFoTFc4TFlfdzFqTEV2WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1RWGhJTXZiaFNNZkZPSnFGUnpwRjJGZmk2TTJZSDJ3NVZwaVJ6eVZndlZnd19tdnFObVZraUdjZ05qTVJNXzc3d0RKSm9hclhxSkNTQzlqUG9sbVJrdTNJLW9SOEpXNTJvQU13OXRGSGpiVDFvU1pCb3BTRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 00:19:08 GMT</t>
+          <t>Tue, 28 Jul 2026 07:51:31 GMT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>히트뉴스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[인사] 아주경제</t>
+          <t>[주식] '언더 6000' 코스피 불안에도, 메드팩토는 상한가 찍어</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>중립</t>
+          <t>부정적 (악재)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9HTks4MkdJY0UxVWhrSktCRVF4Z2s2dWZDWE9La2hMd3EzR2MwcHR2U1V4ZjlrTzVBS2d4R0NhSnY2a3VGV19QTkMzZG14YkVRdVc5T1kyVzBtWkg5RHp0eg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5UYXBFdHllelRQY2oxc1hzaTRfX0FzZERLal81M0loa0xPYnJsSG5vMnQ0aEFLWVd6dFByZTlBSVRYeG5aWmNtT2NyOGNWQzRuNWE1c0F2UVV0Q3FkU1hoOVdRbTdjWTV1SE5V?oc=5</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>반도체, 엔비디아</t>
+          <t>AI, 반도체</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>유가, 🔥유가상승수혜</t>
+          <t>🔥유가상승수혜</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -3795,11 +3795,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TIGER 인도니프티50 (+0.41%)</t>
+          <t>TIGER 인도니프티50 (+0.21%)</t>
         </is>
       </c>
     </row>
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01</v>
+        <v>-0.41</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KODEX 미국달러선물 (+0.03%)</t>
+          <t>KODEX 미국달러선물 (-0.4%)</t>
         </is>
       </c>
     </row>
@@ -3825,41 +3825,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.42</v>
+        <v>-2.24</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TIGER 미국S&amp;P500 (-1.42%)</t>
+          <t>TIGER 미국S&amp;P500 (-2.24%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기후/식량(방어)</t>
+          <t>미래자원/배터리</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.95</v>
+        <v>-2.95</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PHO (+1.15%)</t>
+          <t>REMX (+1.79%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>미래자원/배터리</t>
+          <t>기후/식량(방어)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.95</v>
+        <v>-3.19</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REMX (+1.79%)</t>
+          <t>PHO (+1.15%)</t>
         </is>
       </c>
     </row>
@@ -3870,11 +3870,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.41</v>
+        <v>-5.33</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KT&amp;G (+0.99%)</t>
+          <t>TIGER 미국배당다우존스 (+0.32%)</t>
         </is>
       </c>
     </row>
@@ -3885,11 +3885,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.97</v>
+        <v>-6.52</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>삼성바이오로직스 (+0.39%)</t>
+          <t>삼성바이오로직스 (+0.26%)</t>
         </is>
       </c>
     </row>
@@ -3900,11 +3900,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-6.51</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>삼양식품 (-1.56%)</t>
+          <t>삼양식품 (-3.03%)</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3,455원</t>
+          <t>3,435원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>65.8</v>
+        <v>66.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1,630,000원</t>
+          <t>1,550,000원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1,629,000원</t>
+          <t>1,550,000원</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44.8</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4018,16 +4018,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>232,000원</t>
+          <t>220,000원</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>231,750원</t>
+          <t>220,000원</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.8</v>
+        <v>43.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
